--- a/plans/default_mission_plan.xlsx
+++ b/plans/default_mission_plan.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,41 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002A2A2A"/>
-        <bgColor rgb="002A2A2A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2F9FF"/>
-        <bgColor rgb="00F2F9FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFBF0"/>
-        <bgColor rgb="00FFFBF0"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -74,11 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -444,200 +413,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Satellite</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Activity Sequence ID</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Pre Activity Sequence ID</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>최소 pass contact 시간</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>X-Band 여부</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>NEONSAT1</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>TC_히터_온</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>NEONSAT1</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>TM_덤프_X밴드</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>SPACEEYE-T1</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>안테나_전개</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>SPACEEYE-T1</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>배터리_초기화</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Sat_ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Sub</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Min_El</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Required_Cap</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Min_Duration</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Pre_Req_Main</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Sequence_ID</t>
         </is>
       </c>
     </row>

--- a/plans/default_mission_plan.xlsx
+++ b/plans/default_mission_plan.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Mission Plan Constraints" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Mission Constraints" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,28 +434,787 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>Remark</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>Min_El</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Required_Cap</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Min_Duration</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Pre_Req_Main</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Sequence_ID</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NEONSAT1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>First Contact</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TM 확인
+Panel 전개
+TLE update</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>test1</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>CMD</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NEONSAT1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Health check</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EPS / AOCS / S-band 상태 점검</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>test2</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>180</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>First Contact</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NEONSAT1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Configuration check</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Thermal / STX / FCS param 확인</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>test3</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>180</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Health check</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NEONSAT1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>X-band Key update</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>X key update</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>CMD</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Configuration check</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NEONSAT1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1차 지상 촬영</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>시나리오 등록 / 이미징 / 다운로드</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>20</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>400</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>X-band Key update</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NEONSAT1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1차 Cal Maneuver</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>시나리오 등록 / Max logging / AOTM 다운</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>15</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>BOTH</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>300</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1차 지상 촬영</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NEONSAT1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2차 Cal Maneuver</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>시나리오 등록 / Max logging / AOTM 다운</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>15</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>BOTH</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>300</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>1차 Cal Maneuver</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NEONSAT1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>3차 Cal Maneuver</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>시나리오 등록 / Max logging / AOTM 다운</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>15</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>BOTH</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>300</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2차 Cal Maneuver</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NEONSAT1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>FCS Parameter Update</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>FCP 업데이트 (STS-Gyro up)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>CMD</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>180</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>3차 Cal Maneuver</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>NEONSAT1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1차 별촬영</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>시나리오 등록 / Max logging / AOTM 다운</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>20</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>360</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>FCS Parameter Update</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NEONSAT-1A</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>First Contact</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>TM 확인 / Panel 전개 / TLE update</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CMD</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>300</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NEONSAT-1A</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Health check</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EPS / AOCS / S-band 상태 점검</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>180</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>First Contact</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NEONSAT-1A</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Configuration check</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Thermal / STX / FCS param 확인</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>180</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Health check</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NEONSAT-1A</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>X-band Key update</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>X key update</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="n">
+        <v>15</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>CMD</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>120</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Configuration check</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NEONSAT-1A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1차 지상 촬영</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>시나리오 등록 / 이미징 / 다운로드</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="n">
+        <v>20</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>400</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>X-band Key update</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>NEONSAT-1A</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1차 Cal Maneuver</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>시나리오 등록 / Max logging / AOTM 다운</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="n">
+        <v>15</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>BOTH</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>300</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>1차 지상 촬영</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>NEONSAT-1A</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2차 Cal Maneuver</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>시나리오 등록 / Max logging / AOTM 다운</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="n">
+        <v>15</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>BOTH</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>300</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>1차 Cal Maneuver</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>NEONSAT-1A</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>3차 Cal Maneuver</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>시나리오 등록 / Max logging / AOTM 다운</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="n">
+        <v>15</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>BOTH</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>300</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2차 Cal Maneuver</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>NEONSAT-1A</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>FCS Parameter Update</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>FCP 업데이트 (STS-Gyro up)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="n">
+        <v>10</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>CMD</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>180</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>3차 Cal Maneuver</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>NEONSAT-1A</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1차 별촬영</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>시나리오 등록 / Max logging / AOTM 다운</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>20</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>360</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>FCS Parameter Update</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
